--- a/samples/ss_bksi_cbng_ingest.xlsx
+++ b/samples/ss_bksi_cbng_ingest.xlsx
@@ -632,31 +632,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -685,31 +675,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -756,15 +736,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -780,7 +756,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -827,15 +802,11 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -851,7 +822,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -898,19 +868,16 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>1 IBT (unit 3)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -926,7 +893,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -955,35 +921,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1012,35 +969,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1069,31 +1017,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1122,23 +1060,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>single phi</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1154,7 +1085,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1183,31 +1113,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1236,31 +1156,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1289,31 +1199,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1342,31 +1242,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1395,23 +1285,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>single phi</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1427,7 +1310,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1456,23 +1338,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>single phi</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1488,7 +1363,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1517,31 +1391,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1570,17 +1434,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>UP2B 2 (JABAR): SUKATANI Trf 1,2 / STRDA, KSBRU, DAWUAN</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1606,7 +1464,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1635,17 +1492,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>UP2B 2 (JABAR): NEW TAMBUN</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1661,13 +1512,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1774,7 +1623,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SUTT Bekasi - Sumur Recon</t>
@@ -1795,7 +1643,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -1809,8 +1656,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1827,13 +1672,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT Sumur Recon - Halim</t>
@@ -1854,7 +1697,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -1868,8 +1710,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1886,7 +1726,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1917,7 +1756,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -1931,8 +1769,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1949,7 +1785,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1980,7 +1815,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -1994,8 +1828,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2012,7 +1844,6 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2043,7 +1874,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>1</v>
       </c>
@@ -2057,8 +1887,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2075,7 +1903,6 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2106,7 +1933,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -2120,8 +1946,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2138,13 +1962,11 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Pondok Kelapa - Jatiwaringin</t>
@@ -2165,7 +1987,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -2179,8 +2000,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2197,13 +2016,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Jatiwaringin - New Tambun (arah UP2B Jabar)</t>
@@ -2224,7 +2041,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -2238,8 +2054,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2256,13 +2070,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTT Cibinong - Cibubur</t>
@@ -2283,7 +2095,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -2297,8 +2108,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2315,13 +2124,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT Cibinong - Gandaria</t>
@@ -2342,7 +2149,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -2356,8 +2162,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2374,13 +2178,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT Cibubur - Jatirangon</t>
@@ -2401,7 +2203,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -2415,8 +2216,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2433,13 +2232,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTT Gandaria - Cirencas</t>
@@ -2460,7 +2257,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -2474,8 +2270,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2492,7 +2286,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2579,7 +2372,6 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -2593,8 +2385,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2615,7 +2405,6 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -2629,8 +2418,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2651,7 +2438,6 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -2665,8 +2451,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2687,7 +2471,6 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -2701,8 +2484,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2723,7 +2504,6 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -2737,8 +2517,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2759,7 +2537,6 @@
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -2773,8 +2550,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2795,7 +2570,6 @@
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -2809,8 +2583,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2831,7 +2603,6 @@
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -2845,8 +2616,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2925,12 +2694,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Beban GI Pondok Kelapa dipasok SS Tambun 1,2 (UP2B Jawa Barat). 2.Beban GIS Gandaria dipasok SS Cibinong 1,2-Depok 2- Salak-Pratu selama pekerjaan IBT. 3.Looping dengan IBT 1,2 Tambun selama pekerjaan IBT pada sub sistem tersebut. 4.Telah dipasang OLS tahap 1 sd 3 total target 299 MW sesuai buku DS Tahun 2025. 5.Rencana penambahan target OLS tahap 1 sd 3 total target 382 MW sesuai buku DS Tahun 2025</t>
+          <t>1. Beban GI Pondok Kelapa dipasok SS Tambun 1,2 (UP2B Jawa Barat). 2. Beban GIS Gandaria dipasok SS Cibinong 1,2-Depok 2- Salak-Pratu selama pekerjaan IBT. 3. Looping dengan IBT 1,2 Tambun selama pekerjaan IBT pada sub sistem tersebut. 4. Telah dipasang OLS tahap 1 sd 3 total target 299 MW sesuai buku DS Tahun 2025. 5. Rencana penambahan target OLS tahap 1 sd 3 total target 382 MW sesuai buku DS Tahun 2025</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Usulan pengaktifan kembali SUTT 150 kV Bekasi-New Sukatani (diusulkan COD Tahun 2026). Jangka Menengah : 2.Usulan Penambahan IBT-4 Cibinong, diusulkan COD Tahun 2029. 3.Usulan Pembangunan GITET Jatirangon, diusulkan COD Tahun 2029</t>
+          <t>Jangka Pendek : 1. Usulan pengaktifan kembali SUTT 150 kV Bekasi-New Sukatani (diusulkan COD Tahun 2026). Jangka Menengah : 2. Usulan Penambahan IBT-4 Cibinong, diusulkan COD Tahun 2029. 3. Usulan Pembangunan GITET Jatirangon, diusulkan COD Tahun 2029</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2724,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TerjadiOverloadpada SUTT 150 kV Pondok Kelapa- Miniatur dan SUTT 150 kV Miniatur-Jatirangon apabila trip SUTT 150 kV Pondok Kelapa-Jatirangon atau sebaliknya</t>
+          <t>Terjadi Overloadpada SUTT 150 kV Pondok Kelapa- Miniatur dan SUTT 150 kV Miniatur-Jatirangon apabila trip SUTT 150 kV Pondok Kelapa-Jatirangon atau sebaliknya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2965,7 +2734,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Usulan percepatan normalisasi Double Phi sehingga menjadi 2 sirkit pada SUTT 150 kV Pondok Kelapa-Jatirangon, diusulkan COD Tahun 2027. 2.Usulan percepatan normalisasi Double Phi sehingga menjadi 2 Sirkit SUTT 150 kV Pondok Kelapa-Miniatur diusulkan COD Tahun 2027. 3.Usulan percepatan normalisasi Double Phi sehingga 2 Sirkit 150 kV Jatirangon-Miniatur. diusulkan COD Tahun2027</t>
+          <t>Jangka Pendek : 1. Usulan percepatan normalisasi Double Phi sehingga menjadi 2 sirkit pada SUTT 150 kV Pondok Kelapa-Jatirangon, diusulkan COD Tahun 2027. 2. Usulan percepatan normalisasi Double Phi sehingga menjadi 2 Sirkit SUTT 150 kV Pondok Kelapa-Miniatur diusulkan COD Tahun 2027. 3. Usulan percepatan normalisasi Double Phi sehingga 2 Sirkit 150 kV Jatirangon-Miniatur. diusulkan COD Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2764,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.Memindahkan Trafo GI Pondok Kelapa ke Sub Sistem Tambun 1,2. 2.Memindahkan Trafo GI Gandaria ke Sub Sistem Pelabuhan Ratu</t>
+          <t>1. Memindahkan Trafo GI Pondok Kelapa ke Sub Sistem Tambun 1,2. 2. Memindahkan Trafo GI Gandaria ke Sub Sistem Pelabuhan Ratu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
